--- a/results/link-prediction-gcn/Link/0shot/PROTEINS/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/PROTEINS/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.5792±0.0000</t>
+          <t>0.5335±0.0408</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5200±0.0007</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5199±0.0006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5187±0.0028</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5204±0.0010</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5205±0.0012</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5612±0.0063</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5200±0.0006</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5200±0.0006</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5200±0.0006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5579±0.0089</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5417±0.0173</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5203±0.0009</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4810±0.0000</t>
+          <t>0.4939±0.0190</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5264±0.0000</t>
+          <t>0.5685±0.0016</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5187±0.0000</t>
+          <t>0.5460±0.0076</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5180±0.0009</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5206±0.0003</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5238±0.0029</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5268±0.0000</t>
+          <t>0.5603±0.0056</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5202±0.0004</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5202±0.0004</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5202±0.0004</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5602±0.0017</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5199±0.0007</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5213±0.0026</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4807±0.0000</t>
+          <t>0.5492±0.0711</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5575±0.0010</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5322±0.0167</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5615±0.0000</t>
+          <t>0.5359±0.0113</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5250±0.0000</t>
+          <t>0.5266±0.0027</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5434±0.0000</t>
+          <t>0.5344±0.0160</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5524±0.0102</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5446±0.0000</t>
+          <t>0.5433±0.0028</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5446±0.0000</t>
+          <t>0.5433±0.0028</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5446±0.0000</t>
+          <t>0.5433±0.0028</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5319±0.0000</t>
+          <t>0.5200±0.0007</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5651±0.0000</t>
+          <t>0.5668±0.0044</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5392±0.0000</t>
+          <t>0.5417±0.0010</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.4939±0.0190</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5546±0.0000</t>
+          <t>0.5456±0.0037</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5279±0.0120</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5327±0.0000</t>
+          <t>0.5298±0.0006</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5478±0.0000</t>
+          <t>0.5450±0.0029</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5582±0.0000</t>
+          <t>0.5400±0.0143</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5540±0.0000</t>
+          <t>0.5558±0.0077</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5569±0.0000</t>
+          <t>0.5443±0.0142</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5569±0.0000</t>
+          <t>0.5443±0.0142</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5569±0.0000</t>
+          <t>0.5443±0.0142</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5510±0.0000</t>
+          <t>0.5490±0.0048</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5521±0.0000</t>
+          <t>0.5494±0.0029</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5281±0.0000</t>
+          <t>0.5383±0.0048</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.5677±0.0000</t>
+          <t>0.5505±0.0506</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5187±0.0000</t>
+          <t>0.5518±0.0030</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5248±0.0045</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5221±0.0015</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5200±0.0005</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5198±0.0006</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5531±0.0093</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5276±0.0093</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5285±0.0105</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5285±0.0106</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5618±0.0047</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5215±0.0000</t>
+          <t>0.5207±0.0007</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5231±0.0036</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5636±0.0596</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5453±0.0175</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5199±0.0007</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5184±0.0013</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5195±0.0000</t>
+          <t>0.5205±0.0009</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5238±0.0000</t>
+          <t>0.5207±0.0009</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5431±0.0170</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5198±0.0005</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5201±0.0007</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5200±0.0006</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5566±0.0023</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5198±0.0007</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5207±0.0013</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4810±0.0000</t>
+          <t>0.4801±0.0007</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5284±0.0000</t>
+          <t>0.5614±0.0022</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5200±0.0005</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5283±0.0000</t>
+          <t>0.5338±0.0128</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5177±0.0000</t>
+          <t>0.5265±0.0052</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5253±0.0074</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5181±0.0000</t>
+          <t>0.5312±0.0147</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5200±0.0026</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5199±0.0026</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5199±0.0026</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5334±0.0000</t>
+          <t>0.5257±0.0039</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5491±0.0214</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5207±0.0010</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.5009±0.0000</t>
+          <t>0.3964±0.2905</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6833±0.0000</t>
+          <t>0.6841±0.0006</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6841±0.0005</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6787±0.0036</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6840±0.0005</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6835±0.0000</t>
+          <t>0.6835±0.0006</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6568±0.0071</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6837±0.0002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6837±0.0002</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6837±0.0002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6619±0.0127</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6780±0.0000</t>
+          <t>0.6712±0.0145</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.6837±0.0007</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>0.2283±0.3228</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6657±0.0022</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6801±0.0043</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0029</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6839±0.0004</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6835±0.0011</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6606±0.0118</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0006</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0006</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0006</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6579±0.0071</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.6841±0.0006</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6818±0.0019</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.4295±0.3048</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.6453±0.0084</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6807±0.0047</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6823±0.0036</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.6805±0.0034</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6833±0.0020</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6664±0.0051</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6766±0.0012</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6766±0.0012</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6766±0.0012</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6839±0.0004</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6630±0.0029</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0010</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.2283±0.3228</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6660±0.0054</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0044</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0006</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6669±0.0092</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0125</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6593±0.0040</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6653±0.0138</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6653±0.0138</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6653±0.0138</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6602±0.0053</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6484±0.0030</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6808±0.0023</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.4136±0.2965</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6440±0.0089</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6814±0.0026</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6808±0.0022</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0005</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0004</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6541±0.0121</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6846±0.0015</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6846±0.0015</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6847±0.0016</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6637±0.0059</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6826±0.0025</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6835±0.0004</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.4022±0.2841</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6586±0.0187</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6841±0.0006</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6815±0.0020</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.6839±0.0004</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.6839±0.0003</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6758±0.0105</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0004</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0006</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0004</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6569±0.0086</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0007</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6837±0.0005</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.6789±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6831±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6832±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6832±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6723±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6828±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6828±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6828±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.6826±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0010±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6870±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6782±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6790±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6831±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6758±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6758±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6758±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6822±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6718±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6764±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6833±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6741±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6832±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6767±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6780±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6674±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6780±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6772±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6772±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6772±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6817±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.6791±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.6778±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.4468±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6830±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6833±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6790±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6053±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6841±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6834±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6836±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6836±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6836±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6833±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6836±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6772±0.0000</t>
+          <t>0.6507±0.0056</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.6841±0.0006</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6724±0.0000</t>
+          <t>0.6750±0.0034</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6789±0.0000</t>
+          <t>0.6810±0.0015</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6827±0.0013</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6809±0.0000</t>
+          <t>0.6748±0.0068</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6786±0.0000</t>
+          <t>0.6794±0.0008</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6786±0.0000</t>
+          <t>0.6794±0.0008</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6786±0.0000</t>
+          <t>0.6794±0.0008</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6751±0.0000</t>
+          <t>0.6769±0.0040</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6828±0.0000</t>
+          <t>0.6668±0.0119</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6782±0.0000</t>
+          <t>0.6794±0.0007</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6302±0.0000</t>
+          <t>0.6516±0.0282</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4532±0.0000</t>
+          <t>0.4502±0.0025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5000±0.0001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4999±0.0000</t>
+          <t>0.5584±0.0051</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.6131±0.0250</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5925±0.0169</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4375±0.0000</t>
+          <t>0.5679±0.0063</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5003±0.0000</t>
+          <t>0.5837±0.0283</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5003±0.0000</t>
+          <t>0.5837±0.0283</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5003±0.0000</t>
+          <t>0.5837±0.0283</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.4326±0.0000</t>
+          <t>0.5649±0.0052</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5677±0.0000</t>
+          <t>0.5691±0.0074</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5003±0.0000</t>
+          <t>0.5868±0.0202</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5064±0.0000</t>
+          <t>0.5219±0.0238</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.5262±0.0000</t>
+          <t>0.5747±0.0014</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4996±0.0000</t>
+          <t>0.5551±0.0180</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>0.5494±0.0373</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5769±0.0047</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.5798±0.0318</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.5679±0.0066</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5853±0.0058</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5853±0.0058</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5853±0.0058</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.5723±0.0018</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.6199±0.0049</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5676±0.0075</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.6194±0.0859</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5655±0.0042</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.5199±0.0279</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.5478±0.0351</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.5304±0.0259</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.5231±0.0278</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5427±0.0141</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5322±0.0011</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5322±0.0011</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5322±0.0011</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.4967±0.0016</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5915±0.0025</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5577±0.0150</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.5317±0.0448</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5261±0.0031</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5180±0.0251</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5954±0.0137</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5331±0.0037</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5553±0.0138</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5488±0.0192</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5521±0.0126</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5521±0.0126</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.5521±0.0126</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.5285±0.0059</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.5613±0.0045</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.5740±0.0043</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6365±0.0038</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.5478±0.0026</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5442±0.0553</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.6183±0.0238</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6148±0.0294</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6326±0.0362</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.5461±0.0227</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6207±0.0366</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6206±0.0367</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.6207±0.0366</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.5684±0.0096</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.5685±0.0040</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.5965±0.0198</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.6462±0.0068</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.5260±0.0472</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5495±0.0000</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.5485±0.0000</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.5353±0.0000</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.5564±0.0000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.5564±0.0000</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.5564±0.0000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.4795±0.0000</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.6284±0.0000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.5380±0.0000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.5733±0.0000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.4770±0.0000</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.5002±0.0000</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0.5336±0.0000</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.5134±0.0000</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.5384±0.0000</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.4797±0.0000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.5431±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.5431±0.0000</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.5431±0.0000</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.5275±0.0000</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.5936±0.0000</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.5383±0.0000</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.5453±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.5170±0.0000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.5358±0.0000</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.5486±0.0000</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.5438±0.0000</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.5461±0.0000</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.5461±0.0000</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.5461±0.0000</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.5463±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.5974±0.0000</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>0.5477±0.0000</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.6300±0.0000</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.4605±0.0000</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.5611±0.0431</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.5792±0.0213</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.6178±0.0181</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.5314±0.0468</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.6384±0.0119</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.6033±0.0204</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0.6433±0.0193</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.5664±0.0029</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.5699±0.0038</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.5986±0.0109</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.4994±0.0000</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0.5084±0.0000</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.4533±0.0000</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.4478±0.0000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.5682±0.0000</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.5002±0.0000</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>0.6375±0.0000</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.4494±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.5912±0.0000</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.4637±0.0000</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.6056±0.0000</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>0.6056±0.0000</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.6056±0.0000</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.4351±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.5660±0.0000</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.5685±0.0000</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5534±0.0000</t>
+          <t>0.5726±0.0016</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5025±0.0000</t>
+          <t>0.5002±0.0002</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5138±0.0000</t>
+          <t>0.5622±0.0212</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5387±0.0000</t>
+          <t>0.5972±0.0152</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6231±0.0000</t>
+          <t>0.6258±0.0404</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5502±0.0000</t>
+          <t>0.5618±0.0098</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5778±0.0000</t>
+          <t>0.6099±0.0106</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5778±0.0000</t>
+          <t>0.6099±0.0105</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5778±0.0000</t>
+          <t>0.6099±0.0106</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5443±0.0000</t>
+          <t>0.5568±0.0030</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5795±0.0000</t>
+          <t>0.5940±0.0077</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5569±0.0000</t>
+          <t>0.5899±0.0056</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6370±0.0000</t>
+          <t>0.6645±0.0293</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4877±0.0000</t>
+          <t>0.4894±0.0016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5199±0.0007</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5800±0.0120</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5912±0.0251</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5778±0.0097</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4772±0.0000</t>
+          <t>0.5712±0.0045</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5802±0.0221</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5802±0.0221</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5802±0.0221</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4772±0.0000</t>
+          <t>0.5697±0.0023</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5679±0.0000</t>
+          <t>0.5716±0.0045</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.5192±0.0000</t>
+          <t>0.5848±0.0096</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5335±0.0166</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.5246±0.0000</t>
+          <t>0.5727±0.0023</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5566±0.0135</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5655±0.0349</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5545±0.0000</t>
+          <t>0.5793±0.0118</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5535±0.0000</t>
+          <t>0.5799±0.0269</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.5498±0.0000</t>
+          <t>0.5715±0.0033</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5588±0.0000</t>
+          <t>0.5915±0.0065</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5588±0.0000</t>
+          <t>0.5915±0.0065</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5588±0.0000</t>
+          <t>0.5915±0.0065</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5038±0.0000</t>
+          <t>0.5765±0.0027</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6093±0.0000</t>
+          <t>0.6059±0.0017</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.5468±0.0000</t>
+          <t>0.5793±0.0078</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.6144±0.0778</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5704±0.0045</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5309±0.0149</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5325±0.0000</t>
+          <t>0.5551±0.0263</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5260±0.0000</t>
+          <t>0.5380±0.0174</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.5400±0.0000</t>
+          <t>0.5319±0.0139</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.5092±0.0000</t>
+          <t>0.5413±0.0133</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5435±0.0000</t>
+          <t>0.5372±0.0013</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5435±0.0000</t>
+          <t>0.5372±0.0013</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5435±0.0000</t>
+          <t>0.5372±0.0013</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5325±0.0000</t>
+          <t>0.5182±0.0011</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5899±0.0000</t>
+          <t>0.5902±0.0025</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5406±0.0000</t>
+          <t>0.5566±0.0116</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5472±0.0387</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.5312±0.0000</t>
+          <t>0.5229±0.0015</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5316±0.0170</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5279±0.0000</t>
+          <t>0.5985±0.0149</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5380±0.0000</t>
+          <t>0.5376±0.0024</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5453±0.0000</t>
+          <t>0.5553±0.0116</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5327±0.0000</t>
+          <t>0.5478±0.0188</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.5500±0.0084</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.5500±0.0084</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.5500±0.0084</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5415±0.0000</t>
+          <t>0.5288±0.0034</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5905±0.0000</t>
+          <t>0.5678±0.0027</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5515±0.0000</t>
+          <t>0.5642±0.0031</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6394±0.0000</t>
+          <t>0.6487±0.0061</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.4905±0.0000</t>
+          <t>0.5487±0.0020</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5571±0.0475</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5187±0.0000</t>
+          <t>0.6303±0.0213</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5995±0.0222</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.6172±0.0500</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.4863±0.0000</t>
+          <t>0.5525±0.0166</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.6129±0.0464</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.6129±0.0464</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.6129±0.0464</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.4824±0.0000</t>
+          <t>0.5696±0.0103</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5697±0.0000</t>
+          <t>0.5716±0.0027</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5797±0.0136</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6461±0.0000</t>
+          <t>0.6582±0.0088</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.4841±0.0000</t>
+          <t>0.5379±0.0309</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5199±0.0007</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5887±0.0486</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.5193±0.0000</t>
+          <t>0.5724±0.0125</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5832±0.0000</t>
+          <t>0.6025±0.0142</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.4881±0.0000</t>
+          <t>0.5400±0.0323</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6055±0.0000</t>
+          <t>0.6490±0.0164</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6055±0.0000</t>
+          <t>0.5998±0.0268</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6055±0.0000</t>
+          <t>0.6471±0.0324</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.4774±0.0000</t>
+          <t>0.5697±0.0061</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.5677±0.0000</t>
+          <t>0.5735±0.0042</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.5703±0.0000</t>
+          <t>0.5938±0.0046</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5199±0.0007</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5579±0.0000</t>
+          <t>0.5764±0.0022</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5203±0.0000</t>
+          <t>0.5200±0.0006</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5262±0.0000</t>
+          <t>0.5738±0.0315</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5477±0.0000</t>
+          <t>0.6015±0.0181</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6016±0.0000</t>
+          <t>0.6222±0.0310</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.5704±0.0075</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5840±0.0000</t>
+          <t>0.6032±0.0066</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5840±0.0000</t>
+          <t>0.6032±0.0066</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5840±0.0000</t>
+          <t>0.6032±0.0066</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5474±0.0000</t>
+          <t>0.5619±0.0039</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5785±0.0000</t>
+          <t>0.5949±0.0081</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5618±0.0000</t>
+          <t>0.5945±0.0052</t>
         </is>
       </c>
     </row>
